--- a/Dataset/1_label/DOWN_DOWN_V3_17 divisions_per_second.xlsx
+++ b/Dataset/1_label/DOWN_DOWN_V3_17 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2430,6 +2430,60 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V3_17 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V3_17 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>24200</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V3_17 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
